--- a/data/raw/inventory/Week 27/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 27/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F44" t="n">
         <v>6</v>
@@ -3133,7 +3133,7 @@
         <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
         <v>7</v>
@@ -3201,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>90</v>
       </c>
       <c r="F46" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K46" t="n">
         <v>92</v>
@@ -3313,13 +3313,13 @@
         <v>39</v>
       </c>
       <c r="F47" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -3685,7 +3685,7 @@
         <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
         <v>2</v>
@@ -4119,13 +4119,13 @@
         <v>12</v>
       </c>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G60" t="n">
         <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -4677,13 +4677,13 @@
         <v>22</v>
       </c>
       <c r="F69" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F70" t="n">
         <v>4</v>
@@ -4751,10 +4751,10 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
         <v>5</v>
@@ -5185,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -7343,13 +7343,13 @@
         <v>4</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F136" t="n">
         <v>18</v>
@@ -8837,7 +8837,7 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
@@ -8846,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="K136" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>2</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -9947,13 +9947,13 @@
         <v>2</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -10505,13 +10505,13 @@
         <v>8</v>
       </c>
       <c r="F163" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
@@ -10691,13 +10691,13 @@
         <v>13</v>
       </c>
       <c r="F166" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
@@ -10750,16 +10750,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F167" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -10768,7 +10768,7 @@
         <v>3</v>
       </c>
       <c r="K167" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -10877,13 +10877,13 @@
         <v>15</v>
       </c>
       <c r="F169" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -10939,13 +10939,13 @@
         <v>23</v>
       </c>
       <c r="F170" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -11379,7 +11379,7 @@
         <v>5</v>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
@@ -11388,7 +11388,7 @@
         <v>1</v>
       </c>
       <c r="K177" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
@@ -13171,13 +13171,13 @@
         <v>5</v>
       </c>
       <c r="F206" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
@@ -13357,13 +13357,13 @@
         <v>6</v>
       </c>
       <c r="F209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G209" t="n">
         <v>2</v>
       </c>
       <c r="H209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
@@ -15152,10 +15152,10 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="F238" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -15167,10 +15167,10 @@
         <v>5</v>
       </c>
       <c r="J238" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K238" t="n">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -15651,7 +15651,7 @@
         <v>151</v>
       </c>
       <c r="F246" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -15663,7 +15663,7 @@
         <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K246" t="n">
         <v>151</v>
@@ -15710,7 +15710,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F247" t="n">
         <v>24</v>
@@ -15719,16 +15719,16 @@
         <v>10</v>
       </c>
       <c r="H247" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I247" t="n">
         <v>0</v>
       </c>
       <c r="J247" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K247" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L247" t="n">
         <v>1</v>
@@ -16271,7 +16271,7 @@
         <v>285</v>
       </c>
       <c r="F256" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -16283,7 +16283,7 @@
         <v>0</v>
       </c>
       <c r="J256" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K256" t="n">
         <v>285</v>
@@ -16392,7 +16392,7 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F258" t="n">
         <v>17</v>
@@ -16401,7 +16401,7 @@
         <v>6</v>
       </c>
       <c r="H258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I258" t="n">
         <v>0</v>
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="K258" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L258" t="n">
         <v>1</v>
@@ -16953,7 +16953,7 @@
         <v>2</v>
       </c>
       <c r="F267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -16965,7 +16965,7 @@
         <v>0</v>
       </c>
       <c r="J267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K267" t="n">
         <v>2</v>
@@ -17263,7 +17263,7 @@
         <v>149</v>
       </c>
       <c r="F272" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -17275,7 +17275,7 @@
         <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K272" t="n">
         <v>149</v>
@@ -17573,13 +17573,13 @@
         <v>34</v>
       </c>
       <c r="F277" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G277" t="n">
         <v>15</v>
       </c>
       <c r="H277" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I277" t="n">
         <v>0</v>
@@ -17818,10 +17818,10 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F281" t="n">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -17833,10 +17833,10 @@
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K281" t="n">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L281" t="n">
         <v>2</v>
@@ -17883,7 +17883,7 @@
         <v>638</v>
       </c>
       <c r="F282" t="n">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
@@ -17895,7 +17895,7 @@
         <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K282" t="n">
         <v>638</v>
@@ -18069,7 +18069,7 @@
         <v>494</v>
       </c>
       <c r="F285" t="n">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="G285" t="n">
         <v>0</v>
@@ -18081,7 +18081,7 @@
         <v>1</v>
       </c>
       <c r="J285" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K285" t="n">
         <v>496</v>
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F286" t="n">
         <v>4</v>
@@ -18137,7 +18137,7 @@
         <v>0</v>
       </c>
       <c r="H286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I286" t="n">
         <v>0</v>
@@ -18146,7 +18146,7 @@
         <v>0</v>
       </c>
       <c r="K286" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -18503,13 +18503,13 @@
         <v>27</v>
       </c>
       <c r="F292" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G292" t="n">
         <v>3</v>
       </c>
       <c r="H292" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I292" t="n">
         <v>0</v>
@@ -18689,7 +18689,7 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G295" t="n">
         <v>0</v>
@@ -18701,7 +18701,7 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K295" t="n">
         <v>7</v>
@@ -19495,19 +19495,19 @@
         <v>1</v>
       </c>
       <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
         <v>1</v>
-      </c>
-      <c r="G308" t="n">
-        <v>0</v>
-      </c>
-      <c r="H308" t="n">
-        <v>0</v>
-      </c>
-      <c r="I308" t="n">
-        <v>0</v>
-      </c>
-      <c r="J308" t="n">
-        <v>0</v>
       </c>
       <c r="K308" t="n">
         <v>1</v>
@@ -22843,7 +22843,7 @@
         <v>33</v>
       </c>
       <c r="F362" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G362" t="n">
         <v>0</v>
@@ -22855,7 +22855,7 @@
         <v>0</v>
       </c>
       <c r="J362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K362" t="n">
         <v>34</v>
@@ -23212,7 +23212,7 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F368" t="n">
         <v>7</v>
@@ -23227,10 +23227,10 @@
         <v>0</v>
       </c>
       <c r="J368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K368" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -23835,13 +23835,13 @@
         <v>8</v>
       </c>
       <c r="F378" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G378" t="n">
         <v>2</v>
       </c>
       <c r="H378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I378" t="n">
         <v>0</v>
@@ -23903,13 +23903,13 @@
         <v>0</v>
       </c>
       <c r="H379" t="n">
+        <v>0</v>
+      </c>
+      <c r="I379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" t="n">
         <v>1</v>
-      </c>
-      <c r="I379" t="n">
-        <v>0</v>
-      </c>
-      <c r="J379" t="n">
-        <v>0</v>
       </c>
       <c r="K379" t="n">
         <v>6</v>
@@ -24703,7 +24703,7 @@
         <v>17</v>
       </c>
       <c r="F392" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G392" t="n">
         <v>0</v>
@@ -24715,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="J392" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K392" t="n">
         <v>17</v>

--- a/data/raw/inventory/Week 27/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 27/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>15</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
@@ -1589,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -3189,7 +3189,7 @@
         <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>9</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F46" t="n">
         <v>75</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L46" t="n">
         <v>2</v>
@@ -3310,11 +3310,11 @@
         </is>
       </c>
       <c r="E47" t="n">
+        <v>41</v>
+      </c>
+      <c r="F47" t="n">
         <v>39</v>
       </c>
-      <c r="F47" t="n">
-        <v>38</v>
-      </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
@@ -3325,10 +3325,10 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G57" t="n">
         <v>30</v>
@@ -3945,10 +3945,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -4069,10 +4069,10 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>1</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
         <v>7</v>
       </c>
       <c r="F70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -4751,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K70" t="n">
         <v>7</v>
@@ -4863,19 +4863,19 @@
         <v>1</v>
       </c>
       <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
         <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>1</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F82" t="n">
         <v>33</v>
@@ -5495,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L82" t="n">
         <v>1</v>
@@ -5855,7 +5855,7 @@
         <v>19</v>
       </c>
       <c r="F88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>19</v>
@@ -8273,7 +8273,7 @@
         <v>5</v>
       </c>
       <c r="F127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" t="n">
         <v>5</v>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F135" t="n">
         <v>45</v>
@@ -8781,10 +8781,10 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K135" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -8828,10 +8828,10 @@
         </is>
       </c>
       <c r="E136" t="n">
+        <v>20</v>
+      </c>
+      <c r="F136" t="n">
         <v>19</v>
-      </c>
-      <c r="F136" t="n">
-        <v>18</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -8846,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="K136" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -10505,7 +10505,7 @@
         <v>8</v>
       </c>
       <c r="F163" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -10517,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K163" t="n">
         <v>8</v>
@@ -10688,7 +10688,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F166" t="n">
         <v>12</v>
@@ -10703,10 +10703,10 @@
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -10750,10 +10750,10 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F167" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -10768,7 +10768,7 @@
         <v>3</v>
       </c>
       <c r="K167" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -10998,10 +10998,10 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F171" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G171" t="n">
         <v>12</v>
@@ -11013,10 +11013,10 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K171" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -11370,10 +11370,10 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
         <v>5</v>
@@ -11388,7 +11388,7 @@
         <v>1</v>
       </c>
       <c r="K177" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
@@ -12238,7 +12238,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F191" t="n">
         <v>5</v>
@@ -12253,10 +12253,10 @@
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F195" t="n">
         <v>9</v>
@@ -12501,10 +12501,10 @@
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -13416,10 +13416,10 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G210" t="n">
         <v>7</v>
@@ -13434,7 +13434,7 @@
         <v>1</v>
       </c>
       <c r="K210" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L210" t="n">
         <v>1</v>
@@ -15152,25 +15152,25 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="F238" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I238" t="n">
         <v>5</v>
       </c>
       <c r="J238" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K238" t="n">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -15648,10 +15648,10 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F246" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -15663,10 +15663,10 @@
         <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K246" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F247" t="n">
         <v>24</v>
@@ -15725,10 +15725,10 @@
         <v>0</v>
       </c>
       <c r="J247" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K247" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L247" t="n">
         <v>1</v>
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F250" t="n">
         <v>74</v>
@@ -15911,10 +15911,10 @@
         <v>0</v>
       </c>
       <c r="J250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L250" t="n">
         <v>3</v>
@@ -16268,31 +16268,31 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F256" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I256" t="n">
         <v>0</v>
       </c>
       <c r="J256" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K256" t="n">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N256" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F258" t="n">
         <v>17</v>
@@ -16407,10 +16407,10 @@
         <v>0</v>
       </c>
       <c r="J258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K258" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L258" t="n">
         <v>1</v>
@@ -16767,7 +16767,7 @@
         <v>44</v>
       </c>
       <c r="F264" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G264" t="n">
         <v>6</v>
@@ -16779,7 +16779,7 @@
         <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K264" t="n">
         <v>44</v>
@@ -17508,7 +17508,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F276" t="n">
         <v>200</v>
@@ -17523,10 +17523,10 @@
         <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -17570,10 +17570,10 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F277" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G277" t="n">
         <v>15</v>
@@ -17585,10 +17585,10 @@
         <v>0</v>
       </c>
       <c r="J277" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K277" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L277" t="n">
         <v>1</v>
@@ -17818,25 +17818,25 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>963</v>
+        <v>946</v>
       </c>
       <c r="F281" t="n">
-        <v>738</v>
+        <v>760</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I281" t="n">
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="K281" t="n">
-        <v>965</v>
+        <v>948</v>
       </c>
       <c r="L281" t="n">
         <v>2</v>
@@ -17880,25 +17880,25 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="F282" t="n">
-        <v>589</v>
+        <v>602</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
       </c>
       <c r="H282" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I282" t="n">
         <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K282" t="n">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -18066,25 +18066,25 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="F285" t="n">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="G285" t="n">
         <v>0</v>
       </c>
       <c r="H285" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I285" t="n">
         <v>1</v>
       </c>
       <c r="J285" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K285" t="n">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="L285" t="n">
         <v>2</v>
@@ -18128,10 +18128,10 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F286" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G286" t="n">
         <v>0</v>
@@ -18146,7 +18146,7 @@
         <v>0</v>
       </c>
       <c r="K286" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -18193,7 +18193,7 @@
         <v>5</v>
       </c>
       <c r="F287" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
@@ -18205,7 +18205,7 @@
         <v>0</v>
       </c>
       <c r="J287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K287" t="n">
         <v>5</v>
@@ -18376,7 +18376,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F290" t="n">
         <v>0</v>
@@ -18391,10 +18391,10 @@
         <v>0</v>
       </c>
       <c r="J290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K290" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L290" t="n">
         <v>0</v>
@@ -18875,7 +18875,7 @@
         <v>21</v>
       </c>
       <c r="F298" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G298" t="n">
         <v>0</v>
@@ -18887,7 +18887,7 @@
         <v>0</v>
       </c>
       <c r="J298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K298" t="n">
         <v>21</v>
@@ -18999,19 +18999,19 @@
         <v>1</v>
       </c>
       <c r="F300" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0</v>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
         <v>1</v>
-      </c>
-      <c r="G300" t="n">
-        <v>0</v>
-      </c>
-      <c r="H300" t="n">
-        <v>0</v>
-      </c>
-      <c r="I300" t="n">
-        <v>0</v>
-      </c>
-      <c r="J300" t="n">
-        <v>0</v>
       </c>
       <c r="K300" t="n">
         <v>1</v>
@@ -19058,10 +19058,10 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F301" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G301" t="n">
         <v>3</v>
@@ -19073,10 +19073,10 @@
         <v>0</v>
       </c>
       <c r="J301" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K301" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -19430,10 +19430,10 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F307" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G307" t="n">
         <v>1</v>
@@ -19448,7 +19448,7 @@
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -21910,11 +21910,11 @@
         </is>
       </c>
       <c r="E347" t="n">
+        <v>12</v>
+      </c>
+      <c r="F347" t="n">
         <v>10</v>
       </c>
-      <c r="F347" t="n">
-        <v>6</v>
-      </c>
       <c r="G347" t="n">
         <v>0</v>
       </c>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="J347" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K347" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L347" t="n">
         <v>0</v>
@@ -22905,7 +22905,7 @@
         <v>10</v>
       </c>
       <c r="F363" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G363" t="n">
         <v>0</v>
@@ -22917,7 +22917,7 @@
         <v>0</v>
       </c>
       <c r="J363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K363" t="n">
         <v>10</v>
@@ -23026,7 +23026,7 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F365" t="n">
         <v>11</v>
@@ -23041,10 +23041,10 @@
         <v>0</v>
       </c>
       <c r="J365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K365" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -23150,10 +23150,10 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F367" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G367" t="n">
         <v>0</v>
@@ -23165,10 +23165,10 @@
         <v>0</v>
       </c>
       <c r="J367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L367" t="n">
         <v>0</v>
@@ -24080,10 +24080,10 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
@@ -24098,7 +24098,7 @@
         <v>0</v>
       </c>
       <c r="K382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
@@ -24266,7 +24266,7 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F385" t="n">
         <v>29</v>
@@ -24281,10 +24281,10 @@
         <v>0</v>
       </c>
       <c r="J385" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K385" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L385" t="n">
         <v>0</v>
